--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -27367,10 +27367,10 @@
         </is>
       </c>
       <c r="D1414" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E1414" t="n">
-        <v>5225</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="1415">
@@ -28705,10 +28705,10 @@
         </is>
       </c>
       <c r="D1484" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E1484" t="n">
-        <v>1188</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1485">
@@ -30161,10 +30161,10 @@
         </is>
       </c>
       <c r="D1560" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E1560" t="n">
-        <v>6804</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="1561">
@@ -30864,10 +30864,10 @@
         </is>
       </c>
       <c r="D1597" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E1597" t="n">
-        <v>12306</v>
+        <v>10548</v>
       </c>
     </row>
     <row r="1598">

--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -6906,10 +6906,10 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>-39</v>
+        <v>-37</v>
       </c>
       <c r="E343" t="n">
-        <v>25740</v>
+        <v>24420</v>
       </c>
     </row>
     <row r="344">
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="E354" t="n">
-        <v>24144</v>
+        <v>20120</v>
       </c>
     </row>
     <row r="355">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>-52</v>
+        <v>-49</v>
       </c>
       <c r="E360" t="n">
-        <v>35880</v>
+        <v>33810</v>
       </c>
     </row>
     <row r="361">
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>-38</v>
+        <v>-36</v>
       </c>
       <c r="E361" t="n">
-        <v>31996</v>
+        <v>30312</v>
       </c>
     </row>
     <row r="362">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="E368" t="n">
-        <v>22260</v>
+        <v>21147</v>
       </c>
     </row>
     <row r="369">
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="E376" t="n">
-        <v>24528</v>
+        <v>23360</v>
       </c>
     </row>
     <row r="377">
@@ -10205,10 +10205,10 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="E516" t="n">
-        <v>23240</v>
+        <v>22078</v>
       </c>
     </row>
     <row r="517">
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="D700" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="E700" t="n">
-        <v>10766</v>
+        <v>9997</v>
       </c>
     </row>
     <row r="701">
@@ -13793,10 +13793,10 @@
         </is>
       </c>
       <c r="D704" t="n">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="E704" t="n">
-        <v>29419</v>
+        <v>28470</v>
       </c>
     </row>
     <row r="705">
@@ -14002,10 +14002,10 @@
         </is>
       </c>
       <c r="D715" t="n">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="E715" t="n">
-        <v>19320</v>
+        <v>18630</v>
       </c>
     </row>
     <row r="716">
@@ -14553,10 +14553,10 @@
         </is>
       </c>
       <c r="D744" t="n">
-        <v>-48</v>
+        <v>-47</v>
       </c>
       <c r="E744" t="n">
-        <v>35520</v>
+        <v>34780</v>
       </c>
     </row>
     <row r="745">
@@ -14785,10 +14785,10 @@
         </is>
       </c>
       <c r="D756" t="n">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="E756" t="n">
-        <v>31170</v>
+        <v>30131</v>
       </c>
     </row>
     <row r="757">
@@ -15070,10 +15070,10 @@
         </is>
       </c>
       <c r="D771" t="n">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="E771" t="n">
-        <v>22734</v>
+        <v>21892</v>
       </c>
     </row>
     <row r="772">
@@ -15796,10 +15796,10 @@
         </is>
       </c>
       <c r="D809" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="E809" t="n">
-        <v>14546</v>
+        <v>13507</v>
       </c>
     </row>
     <row r="810">
@@ -15872,10 +15872,10 @@
         </is>
       </c>
       <c r="D813" t="n">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="E813" t="n">
-        <v>41800</v>
+        <v>40755</v>
       </c>
     </row>
     <row r="814">
@@ -16005,10 +16005,10 @@
         </is>
       </c>
       <c r="D820" t="n">
-        <v>-24</v>
+        <v>-23</v>
       </c>
       <c r="E820" t="n">
-        <v>14496</v>
+        <v>13892</v>
       </c>
     </row>
     <row r="821">
@@ -16252,10 +16252,10 @@
         </is>
       </c>
       <c r="D833" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E833" t="n">
-        <v>2820</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="834">
@@ -16613,10 +16613,10 @@
         </is>
       </c>
       <c r="D852" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E852" t="n">
-        <v>1335</v>
+        <v>890</v>
       </c>
     </row>
     <row r="853">
@@ -18398,10 +18398,10 @@
         </is>
       </c>
       <c r="D943" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="E943" t="n">
-        <v>4914</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="944">
@@ -19561,10 +19561,10 @@
         </is>
       </c>
       <c r="D1004" t="n">
-        <v>-45</v>
+        <v>-44</v>
       </c>
       <c r="E1004" t="n">
-        <v>52020</v>
+        <v>50864</v>
       </c>
     </row>
     <row r="1005">

--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -17793,10 +17793,10 @@
         </is>
       </c>
       <c r="D912" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="E912" t="n">
-        <v>55650</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="913">

--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -28738,7 +28738,7 @@
         <v>-9</v>
       </c>
       <c r="E1486" t="n">
-        <v>21788</v>
+        <v>24030</v>
       </c>
     </row>
     <row r="1487">
@@ -28776,7 +28776,7 @@
         <v>-4</v>
       </c>
       <c r="E1488" t="n">
-        <v>4329</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="1489">
@@ -28795,7 +28795,7 @@
         <v>-1</v>
       </c>
       <c r="E1489" t="n">
-        <v>5675</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="1490">
@@ -28814,7 +28814,7 @@
         <v>-3</v>
       </c>
       <c r="E1490" t="n">
-        <v>22126</v>
+        <v>31470</v>
       </c>
     </row>
     <row r="1491">
@@ -28833,7 +28833,7 @@
         <v>-2</v>
       </c>
       <c r="E1491" t="n">
-        <v>2101</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="1492">
@@ -28852,7 +28852,7 @@
         <v>-3</v>
       </c>
       <c r="E1492" t="n">
-        <v>23572</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="1493">
@@ -28909,7 +28909,7 @@
         <v>-18</v>
       </c>
       <c r="E1495" t="n">
-        <v>3871</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="1496">
@@ -28928,7 +28928,7 @@
         <v>-9</v>
       </c>
       <c r="E1496" t="n">
-        <v>3158</v>
+        <v>5381</v>
       </c>
     </row>
     <row r="1497">
@@ -28947,7 +28947,7 @@
         <v>-10</v>
       </c>
       <c r="E1497" t="n">
-        <v>531</v>
+        <v>760</v>
       </c>
     </row>
     <row r="1498">
@@ -28966,7 +28966,7 @@
         <v>-4</v>
       </c>
       <c r="E1498" t="n">
-        <v>461</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="1499">
@@ -28985,7 +28985,7 @@
         <v>-18</v>
       </c>
       <c r="E1499" t="n">
-        <v>10058</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="1500">
@@ -29023,7 +29023,7 @@
         <v>-1</v>
       </c>
       <c r="E1501" t="n">
-        <v>2043</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="1502">
@@ -29042,7 +29042,7 @@
         <v>-1</v>
       </c>
       <c r="E1502" t="n">
-        <v>1495</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1503">
@@ -29061,7 +29061,7 @@
         <v>-1</v>
       </c>
       <c r="E1503" t="n">
-        <v>1592</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1504">
@@ -29080,7 +29080,7 @@
         <v>-1</v>
       </c>
       <c r="E1504" t="n">
-        <v>1835</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="1505">
@@ -29099,7 +29099,7 @@
         <v>-10</v>
       </c>
       <c r="E1505" t="n">
-        <v>12248</v>
+        <v>17137</v>
       </c>
     </row>
     <row r="1506">
@@ -29118,7 +29118,7 @@
         <v>-10</v>
       </c>
       <c r="E1506" t="n">
-        <v>4191</v>
+        <v>5444</v>
       </c>
     </row>
     <row r="1507">
@@ -29137,7 +29137,7 @@
         <v>-2</v>
       </c>
       <c r="E1507" t="n">
-        <v>16385</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="1508">

--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -6487,7 +6487,7 @@
         <v>-5</v>
       </c>
       <c r="E321" t="n">
-        <v>11669</v>
+        <v>13350</v>
       </c>
     </row>
     <row r="322">
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="E322" t="n">
-        <v>796</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="323">
@@ -6525,7 +6525,7 @@
         <v>-2</v>
       </c>
       <c r="E323" t="n">
-        <v>1969</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="324">
@@ -6544,7 +6544,7 @@
         <v>-1</v>
       </c>
       <c r="E324" t="n">
-        <v>5675</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="325">
@@ -6563,7 +6563,7 @@
         <v>-7</v>
       </c>
       <c r="E325" t="n">
-        <v>8846</v>
+        <v>9968</v>
       </c>
     </row>
     <row r="326">
@@ -6582,7 +6582,7 @@
         <v>-4</v>
       </c>
       <c r="E326" t="n">
-        <v>20400</v>
+        <v>25960</v>
       </c>
     </row>
     <row r="327">
@@ -6601,7 +6601,7 @@
         <v>-1</v>
       </c>
       <c r="E327" t="n">
-        <v>5572</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="328">
@@ -6639,7 +6639,7 @@
         <v>-12</v>
       </c>
       <c r="E329" t="n">
-        <v>706</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="330">
@@ -6677,7 +6677,7 @@
         <v>-2</v>
       </c>
       <c r="E331" t="n">
-        <v>5894</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="332">
@@ -6696,7 +6696,7 @@
         <v>-15</v>
       </c>
       <c r="E332" t="n">
-        <v>7502</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="333">
@@ -6715,7 +6715,7 @@
         <v>-25</v>
       </c>
       <c r="E333" t="n">
-        <v>1671</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="334">
@@ -6734,7 +6734,7 @@
         <v>-7</v>
       </c>
       <c r="E334" t="n">
-        <v>1921</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="335">
@@ -6753,7 +6753,7 @@
         <v>-4</v>
       </c>
       <c r="E335" t="n">
-        <v>67933</v>
+        <v>79437</v>
       </c>
     </row>
     <row r="336">
@@ -6829,7 +6829,7 @@
         <v>-1</v>
       </c>
       <c r="E339" t="n">
-        <v>1822</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="340">
@@ -6886,7 +6886,7 @@
         <v>-1</v>
       </c>
       <c r="E342" t="n">
-        <v>4118</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="343">
@@ -6905,7 +6905,7 @@
         <v>-15</v>
       </c>
       <c r="E343" t="n">
-        <v>20346</v>
+        <v>26289</v>
       </c>
     </row>
     <row r="344">
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="E461" t="n">
-        <v>22858</v>
+        <v>19741</v>
       </c>
     </row>
     <row r="462">
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="E514" t="n">
-        <v>12468</v>
+        <v>11429</v>
       </c>
     </row>
     <row r="515">
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="E517" t="n">
-        <v>38665</v>
+        <v>37620</v>
       </c>
     </row>
     <row r="518">
@@ -10338,10 +10338,10 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="E523" t="n">
-        <v>18120</v>
+        <v>16912</v>
       </c>
     </row>
     <row r="524">
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="E526" t="n">
-        <v>15156</v>
+        <v>14314</v>
       </c>
     </row>
     <row r="527">
@@ -11980,10 +11980,10 @@
         </is>
       </c>
       <c r="D609" t="n">
-        <v>-44</v>
+        <v>-42</v>
       </c>
       <c r="E609" t="n">
-        <v>26576</v>
+        <v>25368</v>
       </c>
     </row>
     <row r="610">
@@ -12531,10 +12531,10 @@
         </is>
       </c>
       <c r="D638" t="n">
-        <v>-60</v>
+        <v>-58</v>
       </c>
       <c r="E638" t="n">
-        <v>43440</v>
+        <v>41960</v>
       </c>
     </row>
     <row r="639">
@@ -13276,10 +13276,10 @@
         </is>
       </c>
       <c r="D677" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="E677" t="n">
-        <v>12001</v>
+        <v>10910</v>
       </c>
     </row>
     <row r="678">
@@ -15279,10 +15279,10 @@
         </is>
       </c>
       <c r="D782" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="E782" t="n">
-        <v>15582</v>
+        <v>14469</v>
       </c>
     </row>
     <row r="783">
@@ -15469,10 +15469,10 @@
         </is>
       </c>
       <c r="D792" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="E792" t="n">
-        <v>15820</v>
+        <v>14690</v>
       </c>
     </row>
     <row r="793">
@@ -15507,10 +15507,10 @@
         </is>
       </c>
       <c r="D794" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="E794" t="n">
-        <v>12716</v>
+        <v>10472</v>
       </c>
     </row>
     <row r="795">
@@ -65548,10 +65548,10 @@
         </is>
       </c>
       <c r="D3413" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E3413" t="n">
-        <v>5190</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="3414">
@@ -73036,7 +73036,7 @@
         <v>-5</v>
       </c>
       <c r="E3804" t="n">
-        <v>41450</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="3805">
@@ -73055,7 +73055,7 @@
         <v>-3</v>
       </c>
       <c r="E3805" t="n">
-        <v>25272</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="3806">
@@ -73074,7 +73074,7 @@
         <v>-3</v>
       </c>
       <c r="E3806" t="n">
-        <v>25272</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="3807">
@@ -73405,7 +73405,7 @@
         <v>-7</v>
       </c>
       <c r="E3823" t="n">
-        <v>58030</v>
+        <v>58100</v>
       </c>
     </row>
     <row r="3824">
@@ -73424,7 +73424,7 @@
         <v>-3</v>
       </c>
       <c r="E3824" t="n">
-        <v>25272</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="3825">
@@ -73443,7 +73443,7 @@
         <v>-3</v>
       </c>
       <c r="E3825" t="n">
-        <v>25272</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="3826">
@@ -73580,7 +73580,7 @@
         <v>-3</v>
       </c>
       <c r="E3832" t="n">
-        <v>24870</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="3833">
@@ -73599,7 +73599,7 @@
         <v>-3</v>
       </c>
       <c r="E3833" t="n">
-        <v>25272</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="3834">
@@ -73618,7 +73618,7 @@
         <v>-3</v>
       </c>
       <c r="E3834" t="n">
-        <v>25272</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="3835">
@@ -75372,7 +75372,7 @@
         <v>-1</v>
       </c>
       <c r="E3924" t="n">
-        <v>8424</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="3925">
@@ -75391,7 +75391,7 @@
         <v>-2</v>
       </c>
       <c r="E3925" t="n">
-        <v>16848</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="3926">
@@ -75722,7 +75722,7 @@
         <v>-2</v>
       </c>
       <c r="E3942" t="n">
-        <v>16580</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="3943">
@@ -75741,7 +75741,7 @@
         <v>-2</v>
       </c>
       <c r="E3943" t="n">
-        <v>16848</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="3944">
@@ -75760,7 +75760,7 @@
         <v>-1</v>
       </c>
       <c r="E3944" t="n">
-        <v>8424</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="3945">
@@ -75996,7 +75996,7 @@
         <v>-5</v>
       </c>
       <c r="E3956" t="n">
-        <v>41450</v>
+        <v>41500</v>
       </c>
     </row>
     <row r="3957">
@@ -76015,7 +76015,7 @@
         <v>-3</v>
       </c>
       <c r="E3957" t="n">
-        <v>25272</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="3958">
@@ -76034,7 +76034,7 @@
         <v>-4</v>
       </c>
       <c r="E3958" t="n">
-        <v>33696</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="3959">
@@ -76209,7 +76209,7 @@
         <v>-3</v>
       </c>
       <c r="E3967" t="n">
-        <v>24870</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="3968">
@@ -76228,7 +76228,7 @@
         <v>-2</v>
       </c>
       <c r="E3968" t="n">
-        <v>16848</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="3969">
@@ -76247,7 +76247,7 @@
         <v>-2</v>
       </c>
       <c r="E3969" t="n">
-        <v>16848</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="3970">
@@ -76320,10 +76320,10 @@
         </is>
       </c>
       <c r="D3973" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="E3973" t="n">
-        <v>84720</v>
+        <v>74130</v>
       </c>
     </row>
     <row r="3974">
@@ -76426,7 +76426,7 @@
         <v>-1</v>
       </c>
       <c r="E3978" t="n">
-        <v>8290</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="3979">
@@ -76445,7 +76445,7 @@
         <v>-1</v>
       </c>
       <c r="E3979" t="n">
-        <v>8424</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="3980">
@@ -76601,7 +76601,7 @@
         <v>-2</v>
       </c>
       <c r="E3987" t="n">
-        <v>16580</v>
+        <v>16600</v>
       </c>
     </row>
     <row r="3988">
@@ -76620,7 +76620,7 @@
         <v>-1</v>
       </c>
       <c r="E3988" t="n">
-        <v>8424</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="3989">
@@ -76639,7 +76639,7 @@
         <v>-1</v>
       </c>
       <c r="E3989" t="n">
-        <v>8424</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="3990">

--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>-42</v>
+        <v>-39</v>
       </c>
       <c r="E347" t="n">
-        <v>27720</v>
+        <v>25740</v>
       </c>
     </row>
     <row r="348">
@@ -7267,10 +7267,10 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>-70</v>
+        <v>-61</v>
       </c>
       <c r="E362" t="n">
-        <v>42280</v>
+        <v>36844</v>
       </c>
     </row>
     <row r="363">
@@ -7764,7 +7764,7 @@
         <v>-3</v>
       </c>
       <c r="E388" t="n">
-        <v>3426</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="389">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E389" t="n">
-        <v>2350</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="390">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="E412" t="n">
-        <v>19703</v>
+        <v>18666</v>
       </c>
     </row>
     <row r="413">
@@ -8813,7 +8813,7 @@
         <v>-5</v>
       </c>
       <c r="E443" t="n">
-        <v>5926</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="444">
@@ -8832,7 +8832,7 @@
         <v>-5</v>
       </c>
       <c r="E444" t="n">
-        <v>6400</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="445">
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>-79</v>
+        <v>-76</v>
       </c>
       <c r="E448" t="n">
-        <v>56060</v>
+        <v>54200</v>
       </c>
     </row>
     <row r="449">
@@ -9862,7 +9862,7 @@
         <v>-4</v>
       </c>
       <c r="E498" t="n">
-        <v>4676</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="499">
@@ -9881,7 +9881,7 @@
         <v>-4</v>
       </c>
       <c r="E499" t="n">
-        <v>5050</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="500">
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="E533" t="n">
-        <v>38460</v>
+        <v>37178</v>
       </c>
     </row>
     <row r="534">
@@ -10661,10 +10661,10 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="E540" t="n">
-        <v>19114</v>
+        <v>18108</v>
       </c>
     </row>
     <row r="541">
@@ -10683,7 +10683,7 @@
         <v>-3</v>
       </c>
       <c r="E541" t="n">
-        <v>3426</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="542">
@@ -10702,7 +10702,7 @@
         <v>-3</v>
       </c>
       <c r="E542" t="n">
-        <v>3700</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="543">
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="D630" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="E630" t="n">
-        <v>19860</v>
+        <v>18867</v>
       </c>
     </row>
     <row r="631">
@@ -12439,7 +12439,7 @@
         <v>-4</v>
       </c>
       <c r="E633" t="n">
-        <v>4676</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="634">
@@ -12458,7 +12458,7 @@
         <v>-3</v>
       </c>
       <c r="E634" t="n">
-        <v>3700</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="635">
@@ -13048,10 +13048,10 @@
         </is>
       </c>
       <c r="D665" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="E665" t="n">
-        <v>11788</v>
+        <v>10946</v>
       </c>
     </row>
     <row r="666">
@@ -13488,7 +13488,7 @@
         <v>-4</v>
       </c>
       <c r="E688" t="n">
-        <v>4676</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="689">
@@ -13507,7 +13507,7 @@
         <v>-4</v>
       </c>
       <c r="E689" t="n">
-        <v>5050</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="690">
@@ -14537,7 +14537,7 @@
         <v>-4</v>
       </c>
       <c r="E743" t="n">
-        <v>4676</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="744">
@@ -14556,7 +14556,7 @@
         <v>-4</v>
       </c>
       <c r="E744" t="n">
-        <v>5050</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="745">
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="D774" t="n">
-        <v>-45</v>
+        <v>-44</v>
       </c>
       <c r="E774" t="n">
-        <v>31050</v>
+        <v>30360</v>
       </c>
     </row>
     <row r="775">
@@ -15586,7 +15586,7 @@
         <v>-4</v>
       </c>
       <c r="E798" t="n">
-        <v>4676</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="799">
@@ -15605,7 +15605,7 @@
         <v>-4</v>
       </c>
       <c r="E799" t="n">
-        <v>5050</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="800">
@@ -16540,7 +16540,7 @@
         <v>-3</v>
       </c>
       <c r="E848" t="n">
-        <v>3426</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="849">
@@ -16559,7 +16559,7 @@
         <v>-3</v>
       </c>
       <c r="E849" t="n">
-        <v>3700</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="850">

--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -8651,10 +8651,10 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="E434" t="n">
-        <v>111815</v>
+        <v>110770</v>
       </c>
     </row>
     <row r="435">
@@ -9373,10 +9373,10 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="E472" t="n">
-        <v>75280</v>
+        <v>74660</v>
       </c>
     </row>
     <row r="473">
@@ -10270,10 +10270,10 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>-38</v>
+        <v>-36</v>
       </c>
       <c r="E519" t="n">
-        <v>37734</v>
+        <v>35748</v>
       </c>
     </row>
     <row r="520">
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>-46</v>
+        <v>-41</v>
       </c>
       <c r="E547" t="n">
-        <v>27784</v>
+        <v>24764</v>
       </c>
     </row>
     <row r="548">
@@ -10863,10 +10863,10 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="E550" t="n">
-        <v>23576</v>
+        <v>22734</v>
       </c>
     </row>
     <row r="551">
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="D566" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E566" t="n">
-        <v>6750</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="567">
@@ -12699,10 +12699,10 @@
         </is>
       </c>
       <c r="D646" t="n">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="E646" t="n">
-        <v>41013</v>
+        <v>39690</v>
       </c>
     </row>
     <row r="647">

--- a/I Отчет ПРОДАЖИ 09.2026.xlsx
+++ b/I Отчет ПРОДАЖИ 09.2026.xlsx
@@ -7039,10 +7039,10 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>-59</v>
+        <v>-57</v>
       </c>
       <c r="E350" t="n">
-        <v>38940</v>
+        <v>37620</v>
       </c>
     </row>
     <row r="351">
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>-98</v>
+        <v>-96</v>
       </c>
       <c r="E367" t="n">
-        <v>67620</v>
+        <v>66240</v>
       </c>
     </row>
     <row r="368">
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="E379" t="n">
-        <v>29140</v>
+        <v>28200</v>
       </c>
     </row>
     <row r="380">
@@ -7837,10 +7837,10 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E392" t="n">
-        <v>5400</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="393">
@@ -13425,10 +13425,10 @@
         </is>
       </c>
       <c r="D684" t="n">
-        <v>-72</v>
+        <v>-71</v>
       </c>
       <c r="E684" t="n">
-        <v>68328</v>
+        <v>67379</v>
       </c>
     </row>
     <row r="685">
@@ -13634,10 +13634,10 @@
         </is>
       </c>
       <c r="D695" t="n">
-        <v>-100</v>
+        <v>-99</v>
       </c>
       <c r="E695" t="n">
-        <v>69000</v>
+        <v>68310</v>
       </c>
     </row>
     <row r="696">
@@ -13653,10 +13653,10 @@
         </is>
       </c>
       <c r="D696" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="E696" t="n">
-        <v>15998</v>
+        <v>15156</v>
       </c>
     </row>
     <row r="697">
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="D862" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="E862" t="n">
-        <v>21168</v>
+        <v>19845</v>
       </c>
     </row>
     <row r="863">
